--- a/data/raw/banco_alfa_202603.xlsx
+++ b/data/raw/banco_alfa_202603.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="1324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1857" uniqueCount="1335">
   <si>
     <t>Banco Alfa S.A. - Resumen de cuenta</t>
   </si>
@@ -583,6 +583,9 @@
     <t>ACREDITACION GETNET LIQ 391954</t>
   </si>
   <si>
+    <t>TRANSF ENVIADA A SEGUROS PROTECCION SA CUIT 30-39901863-6</t>
+  </si>
+  <si>
     <t>TRANSF RECIBIDA DESPENSA LOS ANDES SRL CUIT 30-23305727-6 CBU 5398997453581342172334</t>
   </si>
   <si>
@@ -691,6 +694,9 @@
     <t>ACREDITACION GETNET LIQ 541776</t>
   </si>
   <si>
+    <t>DEBITO DIRECTO ENERGIA URBANA SA CLIENTE 778812</t>
+  </si>
+  <si>
     <t>TRANSF RECIBIDA LOPEZ HERNAN DARIO CUIT 20-16559687-2 CBU 0807370283822264686164</t>
   </si>
   <si>
@@ -754,6 +760,9 @@
     <t>ACREDITACION GETNET LIQ 305453</t>
   </si>
   <si>
+    <t>REVERSO DEBITO DIRECTO ENERGIA URBANA SA CLIENTE 778812</t>
+  </si>
+  <si>
     <t>TRANSF RECIBIDA MEDINA VALERIA CUIT 20-32680087-1 CBU 5846450604541465908538</t>
   </si>
   <si>
@@ -1471,6 +1480,9 @@
     <t>B810291</t>
   </si>
   <si>
+    <t>B810414</t>
+  </si>
+  <si>
     <t>B810055</t>
   </si>
   <si>
@@ -1657,6 +1669,9 @@
     <t>B810311</t>
   </si>
   <si>
+    <t>B810415</t>
+  </si>
+  <si>
     <t>B810008</t>
   </si>
   <si>
@@ -1762,6 +1777,9 @@
     <t>B810325</t>
   </si>
   <si>
+    <t>B810416</t>
+  </si>
+  <si>
     <t>B810012</t>
   </si>
   <si>
@@ -2212,6 +2230,9 @@
     <t>26.000,59</t>
   </si>
   <si>
+    <t>287.640,00</t>
+  </si>
+  <si>
     <t>207.258,30</t>
   </si>
   <si>
@@ -2314,6 +2335,9 @@
     <t>15.330,33</t>
   </si>
   <si>
+    <t>96.420,50</t>
+  </si>
+  <si>
     <t>4.195,96</t>
   </si>
   <si>
@@ -3601,391 +3625,400 @@
     <t>52.175.366,07</t>
   </si>
   <si>
-    <t>52.693.556,50</t>
-  </si>
-  <si>
-    <t>53.654.616,88</t>
-  </si>
-  <si>
-    <t>53.726.658,13</t>
-  </si>
-  <si>
-    <t>55.355.368,70</t>
-  </si>
-  <si>
-    <t>55.655.368,70</t>
-  </si>
-  <si>
-    <t>55.955.368,70</t>
-  </si>
-  <si>
-    <t>55.748.110,40</t>
-  </si>
-  <si>
-    <t>54.379.641,76</t>
-  </si>
-  <si>
-    <t>54.990.538,31</t>
-  </si>
-  <si>
-    <t>54.987.358,91</t>
-  </si>
-  <si>
-    <t>54.986.691,24</t>
-  </si>
-  <si>
-    <t>54.983.730,89</t>
-  </si>
-  <si>
-    <t>54.983.109,22</t>
-  </si>
-  <si>
-    <t>54.961.173,71</t>
-  </si>
-  <si>
-    <t>54.937.540,94</t>
-  </si>
-  <si>
-    <t>56.154.394,63</t>
-  </si>
-  <si>
-    <t>57.528.504,68</t>
-  </si>
-  <si>
-    <t>59.421.242,80</t>
-  </si>
-  <si>
-    <t>61.055.557,62</t>
-  </si>
-  <si>
-    <t>62.065.685,39</t>
-  </si>
-  <si>
-    <t>64.077.746,30</t>
-  </si>
-  <si>
-    <t>64.980.729,54</t>
-  </si>
-  <si>
-    <t>62.872.680,39</t>
-  </si>
-  <si>
-    <t>63.209.481,61</t>
-  </si>
-  <si>
-    <t>62.260.746,77</t>
-  </si>
-  <si>
-    <t>61.359.878,58</t>
-  </si>
-  <si>
-    <t>59.733.159,82</t>
-  </si>
-  <si>
-    <t>58.572.739,84</t>
-  </si>
-  <si>
-    <t>56.992.795,72</t>
-  </si>
-  <si>
-    <t>56.990.525,94</t>
-  </si>
-  <si>
-    <t>56.990.049,29</t>
-  </si>
-  <si>
-    <t>56.971.907,71</t>
-  </si>
-  <si>
-    <t>56.950.583,13</t>
-  </si>
-  <si>
-    <t>58.034.352,22</t>
-  </si>
-  <si>
-    <t>59.947.080,68</t>
-  </si>
-  <si>
-    <t>60.221.734,27</t>
-  </si>
-  <si>
-    <t>62.553.349,23</t>
-  </si>
-  <si>
-    <t>59.539.262,87</t>
-  </si>
-  <si>
-    <t>57.438.613,15</t>
-  </si>
-  <si>
-    <t>55.714.025,46</t>
-  </si>
-  <si>
-    <t>56.485.551,15</t>
-  </si>
-  <si>
-    <t>56.481.557,13</t>
-  </si>
-  <si>
-    <t>56.480.718,39</t>
-  </si>
-  <si>
-    <t>56.441.246,42</t>
-  </si>
-  <si>
-    <t>56.409.437,74</t>
-  </si>
-  <si>
-    <t>56.386.151,76</t>
-  </si>
-  <si>
-    <t>57.040.257,04</t>
-  </si>
-  <si>
-    <t>58.729.809,02</t>
-  </si>
-  <si>
-    <t>59.384.356,39</t>
-  </si>
-  <si>
-    <t>61.444.021,63</t>
-  </si>
-  <si>
-    <t>61.803.496,25</t>
-  </si>
-  <si>
-    <t>64.050.823,63</t>
-  </si>
-  <si>
-    <t>66.024.456,70</t>
-  </si>
-  <si>
-    <t>64.379.242,51</t>
-  </si>
-  <si>
-    <t>63.291.577,49</t>
-  </si>
-  <si>
-    <t>63.886.906,99</t>
-  </si>
-  <si>
-    <t>63.881.609,29</t>
-  </si>
-  <si>
-    <t>63.880.496,77</t>
-  </si>
-  <si>
-    <t>63.875.953,66</t>
-  </si>
-  <si>
-    <t>63.874.999,61</t>
-  </si>
-  <si>
-    <t>63.841.440,83</t>
-  </si>
-  <si>
-    <t>63.826.110,50</t>
-  </si>
-  <si>
-    <t>64.811.125,40</t>
-  </si>
-  <si>
-    <t>66.659.696,22</t>
-  </si>
-  <si>
-    <t>68.336.594,33</t>
-  </si>
-  <si>
-    <t>69.810.157,89</t>
-  </si>
-  <si>
-    <t>71.984.253,58</t>
-  </si>
-  <si>
-    <t>74.350.676,22</t>
-  </si>
-  <si>
-    <t>76.507.531,18</t>
-  </si>
-  <si>
-    <t>76.604.597,10</t>
-  </si>
-  <si>
-    <t>77.467.267,94</t>
-  </si>
-  <si>
-    <t>77.463.071,98</t>
-  </si>
-  <si>
-    <t>77.462.190,83</t>
-  </si>
-  <si>
-    <t>77.459.462,33</t>
-  </si>
-  <si>
-    <t>77.458.889,34</t>
-  </si>
-  <si>
-    <t>77.429.657,87</t>
-  </si>
-  <si>
-    <t>77.391.968,75</t>
-  </si>
-  <si>
-    <t>77.865.456,29</t>
-  </si>
-  <si>
-    <t>79.775.152,37</t>
-  </si>
-  <si>
-    <t>80.048.788,81</t>
-  </si>
-  <si>
-    <t>80.983.769,58</t>
-  </si>
-  <si>
-    <t>82.606.677,79</t>
-  </si>
-  <si>
-    <t>82.857.509,22</t>
-  </si>
-  <si>
-    <t>83.620.319,06</t>
-  </si>
-  <si>
-    <t>83.875.872,16</t>
-  </si>
-  <si>
-    <t>84.613.701,56</t>
-  </si>
-  <si>
-    <t>83.068.840,94</t>
-  </si>
-  <si>
-    <t>80.578.822,95</t>
-  </si>
-  <si>
-    <t>80.974.713,74</t>
-  </si>
-  <si>
-    <t>80.973.406,82</t>
-  </si>
-  <si>
-    <t>80.973.132,37</t>
-  </si>
-  <si>
-    <t>80.969.123,07</t>
-  </si>
-  <si>
-    <t>80.968.281,12</t>
-  </si>
-  <si>
-    <t>80.961.998,92</t>
-  </si>
-  <si>
-    <t>80.960.679,66</t>
-  </si>
-  <si>
-    <t>80.913.634,43</t>
-  </si>
-  <si>
-    <t>80.874.653,71</t>
-  </si>
-  <si>
-    <t>82.009.241,20</t>
-  </si>
-  <si>
-    <t>82.343.164,87</t>
-  </si>
-  <si>
-    <t>84.425.583,68</t>
-  </si>
-  <si>
-    <t>85.559.116,34</t>
-  </si>
-  <si>
-    <t>86.184.552,71</t>
-  </si>
-  <si>
-    <t>86.182.437,02</t>
-  </si>
-  <si>
-    <t>86.181.992,73</t>
-  </si>
-  <si>
-    <t>86.178.371,31</t>
-  </si>
-  <si>
-    <t>86.177.610,81</t>
-  </si>
-  <si>
-    <t>86.142.502,89</t>
-  </si>
-  <si>
-    <t>86.131.654,09</t>
-  </si>
-  <si>
-    <t>84.231.479,48</t>
-  </si>
-  <si>
-    <t>81.433.865,56</t>
-  </si>
-  <si>
-    <t>78.937.411,36</t>
-  </si>
-  <si>
-    <t>79.138.597,96</t>
-  </si>
-  <si>
-    <t>79.136.987,99</t>
-  </si>
-  <si>
-    <t>79.136.649,90</t>
-  </si>
-  <si>
-    <t>79.131.801,26</t>
-  </si>
-  <si>
-    <t>79.130.783,05</t>
-  </si>
-  <si>
-    <t>79.089.788,37</t>
-  </si>
-  <si>
-    <t>79.077.996,50</t>
-  </si>
-  <si>
-    <t>79.028.651,04</t>
-  </si>
-  <si>
-    <t>77.270.549,40</t>
-  </si>
-  <si>
-    <t>78.152.845,85</t>
-  </si>
-  <si>
-    <t>78.147.387,72</t>
-  </si>
-  <si>
-    <t>78.146.241,51</t>
-  </si>
-  <si>
-    <t>78.140.235,06</t>
-  </si>
-  <si>
-    <t>78.138.973,71</t>
-  </si>
-  <si>
-    <t>78.121.199,88</t>
-  </si>
-  <si>
-    <t>78.102.113,19</t>
-  </si>
-  <si>
-    <t>78.083.613,19</t>
-  </si>
-  <si>
-    <t>78.079.728,19</t>
+    <t>51.887.726,07</t>
+  </si>
+  <si>
+    <t>52.405.916,50</t>
+  </si>
+  <si>
+    <t>53.366.976,88</t>
+  </si>
+  <si>
+    <t>53.439.018,13</t>
+  </si>
+  <si>
+    <t>55.067.728,70</t>
+  </si>
+  <si>
+    <t>55.367.728,70</t>
+  </si>
+  <si>
+    <t>55.667.728,70</t>
+  </si>
+  <si>
+    <t>55.460.470,40</t>
+  </si>
+  <si>
+    <t>54.092.001,76</t>
+  </si>
+  <si>
+    <t>54.702.898,31</t>
+  </si>
+  <si>
+    <t>54.699.718,91</t>
+  </si>
+  <si>
+    <t>54.699.051,24</t>
+  </si>
+  <si>
+    <t>54.696.090,89</t>
+  </si>
+  <si>
+    <t>54.695.469,22</t>
+  </si>
+  <si>
+    <t>54.673.533,71</t>
+  </si>
+  <si>
+    <t>54.649.900,94</t>
+  </si>
+  <si>
+    <t>55.866.754,63</t>
+  </si>
+  <si>
+    <t>57.240.864,68</t>
+  </si>
+  <si>
+    <t>59.133.602,80</t>
+  </si>
+  <si>
+    <t>60.767.917,62</t>
+  </si>
+  <si>
+    <t>61.778.045,39</t>
+  </si>
+  <si>
+    <t>63.790.106,30</t>
+  </si>
+  <si>
+    <t>64.693.089,54</t>
+  </si>
+  <si>
+    <t>62.585.040,39</t>
+  </si>
+  <si>
+    <t>62.921.841,61</t>
+  </si>
+  <si>
+    <t>61.973.106,77</t>
+  </si>
+  <si>
+    <t>61.072.238,58</t>
+  </si>
+  <si>
+    <t>59.445.519,82</t>
+  </si>
+  <si>
+    <t>58.285.099,84</t>
+  </si>
+  <si>
+    <t>56.705.155,72</t>
+  </si>
+  <si>
+    <t>56.702.885,94</t>
+  </si>
+  <si>
+    <t>56.702.409,29</t>
+  </si>
+  <si>
+    <t>56.684.267,71</t>
+  </si>
+  <si>
+    <t>56.662.943,13</t>
+  </si>
+  <si>
+    <t>57.746.712,22</t>
+  </si>
+  <si>
+    <t>59.659.440,68</t>
+  </si>
+  <si>
+    <t>59.934.094,27</t>
+  </si>
+  <si>
+    <t>62.265.709,23</t>
+  </si>
+  <si>
+    <t>59.251.622,87</t>
+  </si>
+  <si>
+    <t>57.150.973,15</t>
+  </si>
+  <si>
+    <t>55.426.385,46</t>
+  </si>
+  <si>
+    <t>56.197.911,15</t>
+  </si>
+  <si>
+    <t>56.193.917,13</t>
+  </si>
+  <si>
+    <t>56.193.078,39</t>
+  </si>
+  <si>
+    <t>56.153.606,42</t>
+  </si>
+  <si>
+    <t>56.121.797,74</t>
+  </si>
+  <si>
+    <t>56.098.511,76</t>
+  </si>
+  <si>
+    <t>56.752.617,04</t>
+  </si>
+  <si>
+    <t>58.442.169,02</t>
+  </si>
+  <si>
+    <t>59.096.716,39</t>
+  </si>
+  <si>
+    <t>61.156.381,63</t>
+  </si>
+  <si>
+    <t>61.515.856,25</t>
+  </si>
+  <si>
+    <t>63.763.183,63</t>
+  </si>
+  <si>
+    <t>65.736.816,70</t>
+  </si>
+  <si>
+    <t>64.091.602,51</t>
+  </si>
+  <si>
+    <t>63.003.937,49</t>
+  </si>
+  <si>
+    <t>63.599.266,99</t>
+  </si>
+  <si>
+    <t>63.593.969,29</t>
+  </si>
+  <si>
+    <t>63.592.856,77</t>
+  </si>
+  <si>
+    <t>63.588.313,66</t>
+  </si>
+  <si>
+    <t>63.587.359,61</t>
+  </si>
+  <si>
+    <t>63.553.800,83</t>
+  </si>
+  <si>
+    <t>63.538.470,50</t>
+  </si>
+  <si>
+    <t>63.442.050,00</t>
+  </si>
+  <si>
+    <t>64.427.064,90</t>
+  </si>
+  <si>
+    <t>66.275.635,72</t>
+  </si>
+  <si>
+    <t>67.952.533,83</t>
+  </si>
+  <si>
+    <t>69.426.097,39</t>
+  </si>
+  <si>
+    <t>71.600.193,08</t>
+  </si>
+  <si>
+    <t>73.966.615,72</t>
+  </si>
+  <si>
+    <t>76.123.470,68</t>
+  </si>
+  <si>
+    <t>76.220.536,60</t>
+  </si>
+  <si>
+    <t>77.083.207,44</t>
+  </si>
+  <si>
+    <t>77.079.011,48</t>
+  </si>
+  <si>
+    <t>77.078.130,33</t>
+  </si>
+  <si>
+    <t>77.075.401,83</t>
+  </si>
+  <si>
+    <t>77.074.828,84</t>
+  </si>
+  <si>
+    <t>77.045.597,37</t>
+  </si>
+  <si>
+    <t>77.007.908,25</t>
+  </si>
+  <si>
+    <t>77.481.395,79</t>
+  </si>
+  <si>
+    <t>79.391.091,87</t>
+  </si>
+  <si>
+    <t>79.664.728,31</t>
+  </si>
+  <si>
+    <t>80.599.709,08</t>
+  </si>
+  <si>
+    <t>82.222.617,29</t>
+  </si>
+  <si>
+    <t>82.473.448,72</t>
+  </si>
+  <si>
+    <t>83.236.258,56</t>
+  </si>
+  <si>
+    <t>83.491.811,66</t>
+  </si>
+  <si>
+    <t>84.229.641,06</t>
+  </si>
+  <si>
+    <t>82.684.780,44</t>
+  </si>
+  <si>
+    <t>80.194.762,45</t>
+  </si>
+  <si>
+    <t>80.590.653,24</t>
+  </si>
+  <si>
+    <t>80.589.346,32</t>
+  </si>
+  <si>
+    <t>80.589.071,87</t>
+  </si>
+  <si>
+    <t>80.585.062,57</t>
+  </si>
+  <si>
+    <t>80.584.220,62</t>
+  </si>
+  <si>
+    <t>80.577.938,42</t>
+  </si>
+  <si>
+    <t>80.576.619,16</t>
+  </si>
+  <si>
+    <t>80.529.573,93</t>
+  </si>
+  <si>
+    <t>80.490.593,21</t>
+  </si>
+  <si>
+    <t>80.587.013,71</t>
+  </si>
+  <si>
+    <t>81.721.601,20</t>
+  </si>
+  <si>
+    <t>82.055.524,87</t>
+  </si>
+  <si>
+    <t>84.137.943,68</t>
+  </si>
+  <si>
+    <t>85.271.476,34</t>
+  </si>
+  <si>
+    <t>85.896.912,71</t>
+  </si>
+  <si>
+    <t>85.894.797,02</t>
+  </si>
+  <si>
+    <t>85.894.352,73</t>
+  </si>
+  <si>
+    <t>85.890.731,31</t>
+  </si>
+  <si>
+    <t>85.889.970,81</t>
+  </si>
+  <si>
+    <t>85.854.862,89</t>
+  </si>
+  <si>
+    <t>85.844.014,09</t>
+  </si>
+  <si>
+    <t>83.943.839,48</t>
+  </si>
+  <si>
+    <t>81.146.225,56</t>
+  </si>
+  <si>
+    <t>78.649.771,36</t>
+  </si>
+  <si>
+    <t>78.850.957,96</t>
+  </si>
+  <si>
+    <t>78.849.347,99</t>
+  </si>
+  <si>
+    <t>78.849.009,90</t>
+  </si>
+  <si>
+    <t>78.844.161,26</t>
+  </si>
+  <si>
+    <t>78.843.143,05</t>
+  </si>
+  <si>
+    <t>78.802.148,37</t>
+  </si>
+  <si>
+    <t>78.790.356,50</t>
+  </si>
+  <si>
+    <t>78.741.011,04</t>
+  </si>
+  <si>
+    <t>76.982.909,40</t>
+  </si>
+  <si>
+    <t>77.865.205,85</t>
+  </si>
+  <si>
+    <t>77.859.747,72</t>
+  </si>
+  <si>
+    <t>77.858.601,51</t>
+  </si>
+  <si>
+    <t>77.852.595,06</t>
+  </si>
+  <si>
+    <t>77.851.333,71</t>
+  </si>
+  <si>
+    <t>77.833.559,88</t>
+  </si>
+  <si>
+    <t>77.814.473,19</t>
+  </si>
+  <si>
+    <t>77.795.973,19</t>
+  </si>
+  <si>
+    <t>77.792.088,19</t>
   </si>
 </sst>
 </file>
@@ -4317,7 +4350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F375"/>
+  <dimension ref="A1:F378"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4343,16 +4376,16 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D4" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="E4" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="F4" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4363,13 +4396,13 @@
         <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E5" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="F5" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4380,13 +4413,13 @@
         <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E6" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="F6" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4397,13 +4430,13 @@
         <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E7" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="F7" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4414,13 +4447,13 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E8" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="F8" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4431,13 +4464,13 @@
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E9" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="F9" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4448,13 +4481,13 @@
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E10" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="F10" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4465,13 +4498,13 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E11" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="F11" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4482,13 +4515,13 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D12" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="F12" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4499,13 +4532,13 @@
         <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E13" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="F13" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4516,13 +4549,13 @@
         <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D14" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="F14" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4533,13 +4566,13 @@
         <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D15" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="F15" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4550,13 +4583,13 @@
         <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D16" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="F16" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4567,13 +4600,13 @@
         <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D17" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="F17" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4584,13 +4617,13 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D18" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="F18" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4601,13 +4634,13 @@
         <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E19" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="F19" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4618,13 +4651,13 @@
         <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E20" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="F20" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4635,13 +4668,13 @@
         <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E21" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="F21" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4652,13 +4685,13 @@
         <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E22" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="F22" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4669,13 +4702,13 @@
         <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E23" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="F23" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -4686,13 +4719,13 @@
         <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D24" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="F24" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4703,13 +4736,13 @@
         <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D25" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F25" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4720,13 +4753,13 @@
         <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D26" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="F26" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4737,13 +4770,13 @@
         <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D27" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="F27" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4754,13 +4787,13 @@
         <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E28" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="F28" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4771,13 +4804,13 @@
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D29" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="F29" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4788,13 +4821,13 @@
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D30" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="F30" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4805,13 +4838,13 @@
         <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D31" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="F31" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4822,13 +4855,13 @@
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D32" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="F32" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4839,13 +4872,13 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E33" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="F33" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4856,13 +4889,13 @@
         <v>62</v>
       </c>
       <c r="C34" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E34" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="F34" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4873,13 +4906,13 @@
         <v>63</v>
       </c>
       <c r="C35" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E35" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="F35" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -4890,13 +4923,13 @@
         <v>64</v>
       </c>
       <c r="C36" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E36" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="F36" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -4907,13 +4940,13 @@
         <v>65</v>
       </c>
       <c r="C37" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E37" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="F37" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4924,13 +4957,13 @@
         <v>66</v>
       </c>
       <c r="C38" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E38" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="F38" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4941,13 +4974,13 @@
         <v>67</v>
       </c>
       <c r="C39" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E39" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="F39" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4958,13 +4991,13 @@
         <v>68</v>
       </c>
       <c r="C40" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E40" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="F40" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -4975,13 +5008,13 @@
         <v>69</v>
       </c>
       <c r="C41" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D41" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="F41" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -4992,13 +5025,13 @@
         <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E42" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="F42" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -5009,13 +5042,13 @@
         <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D43" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="F43" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -5026,13 +5059,13 @@
         <v>47</v>
       </c>
       <c r="C44" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D44" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="F44" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -5043,13 +5076,13 @@
         <v>46</v>
       </c>
       <c r="C45" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D45" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="F45" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -5060,13 +5093,13 @@
         <v>47</v>
       </c>
       <c r="C46" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D46" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="F46" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -5077,13 +5110,13 @@
         <v>48</v>
       </c>
       <c r="C47" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D47" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="F47" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -5094,13 +5127,13 @@
         <v>49</v>
       </c>
       <c r="C48" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D48" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="F48" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -5111,13 +5144,13 @@
         <v>71</v>
       </c>
       <c r="C49" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E49" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="F49" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -5125,7 +5158,7 @@
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -5136,16 +5169,16 @@
         <v>36</v>
       </c>
       <c r="C51" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="E51" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="F51" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -5156,13 +5189,13 @@
         <v>72</v>
       </c>
       <c r="C52" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E52" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="F52" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -5173,13 +5206,13 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E53" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="F53" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -5190,13 +5223,13 @@
         <v>74</v>
       </c>
       <c r="C54" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E54" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="F54" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -5207,13 +5240,13 @@
         <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E55" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="F55" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -5224,13 +5257,13 @@
         <v>76</v>
       </c>
       <c r="C56" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E56" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="F56" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -5241,13 +5274,13 @@
         <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E57" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="F57" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -5258,13 +5291,13 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E58" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="F58" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -5275,13 +5308,13 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D59" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="F59" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -5292,13 +5325,13 @@
         <v>80</v>
       </c>
       <c r="C60" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D60" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="F60" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -5309,13 +5342,13 @@
         <v>81</v>
       </c>
       <c r="C61" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D61" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="F61" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -5326,13 +5359,13 @@
         <v>82</v>
       </c>
       <c r="C62" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E62" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="F62" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -5343,13 +5376,13 @@
         <v>83</v>
       </c>
       <c r="C63" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D63" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="F63" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -5360,13 +5393,13 @@
         <v>84</v>
       </c>
       <c r="C64" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D64" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="F64" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5377,13 +5410,13 @@
         <v>85</v>
       </c>
       <c r="C65" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D65" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="F65" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -5394,13 +5427,13 @@
         <v>86</v>
       </c>
       <c r="C66" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D66" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="F66" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5411,13 +5444,13 @@
         <v>87</v>
       </c>
       <c r="C67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D67" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="F67" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5428,13 +5461,13 @@
         <v>46</v>
       </c>
       <c r="C68" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D68" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="F68" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -5445,13 +5478,13 @@
         <v>47</v>
       </c>
       <c r="C69" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D69" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="F69" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -5462,13 +5495,13 @@
         <v>48</v>
       </c>
       <c r="C70" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D70" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="F70" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -5479,13 +5512,13 @@
         <v>49</v>
       </c>
       <c r="C71" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D71" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F71" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5496,13 +5529,13 @@
         <v>88</v>
       </c>
       <c r="C72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E72" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="F72" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -5513,13 +5546,13 @@
         <v>89</v>
       </c>
       <c r="C73" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E73" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="F73" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5530,13 +5563,13 @@
         <v>90</v>
       </c>
       <c r="C74" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E74" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="F74" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5547,13 +5580,13 @@
         <v>91</v>
       </c>
       <c r="C75" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E75" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="F75" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -5564,13 +5597,13 @@
         <v>92</v>
       </c>
       <c r="C76" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E76" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="F76" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -5581,13 +5614,13 @@
         <v>93</v>
       </c>
       <c r="C77" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E77" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="F77" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -5598,13 +5631,13 @@
         <v>94</v>
       </c>
       <c r="C78" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E78" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="F78" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -5615,13 +5648,13 @@
         <v>95</v>
       </c>
       <c r="C79" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E79" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="F79" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -5632,13 +5665,13 @@
         <v>96</v>
       </c>
       <c r="C80" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D80" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="F80" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -5649,13 +5682,13 @@
         <v>97</v>
       </c>
       <c r="C81" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E81" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="F81" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -5666,13 +5699,13 @@
         <v>46</v>
       </c>
       <c r="C82" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D82" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="F82" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -5683,13 +5716,13 @@
         <v>47</v>
       </c>
       <c r="C83" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D83" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="F83" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -5700,13 +5733,13 @@
         <v>46</v>
       </c>
       <c r="C84" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D84" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="F84" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5717,13 +5750,13 @@
         <v>47</v>
       </c>
       <c r="C85" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D85" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="F85" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -5734,13 +5767,13 @@
         <v>46</v>
       </c>
       <c r="C86" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D86" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="F86" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5751,13 +5784,13 @@
         <v>47</v>
       </c>
       <c r="C87" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D87" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="F87" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -5768,13 +5801,13 @@
         <v>48</v>
       </c>
       <c r="C88" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D88" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="F88" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -5785,13 +5818,13 @@
         <v>49</v>
       </c>
       <c r="C89" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D89" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="F89" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -5802,13 +5835,13 @@
         <v>98</v>
       </c>
       <c r="C90" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E90" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="F90" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -5819,13 +5852,13 @@
         <v>99</v>
       </c>
       <c r="C91" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E91" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F91" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -5836,13 +5869,13 @@
         <v>100</v>
       </c>
       <c r="C92" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E92" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="F92" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -5853,13 +5886,13 @@
         <v>101</v>
       </c>
       <c r="C93" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E93" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="F93" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -5870,13 +5903,13 @@
         <v>102</v>
       </c>
       <c r="C94" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E94" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="F94" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -5887,13 +5920,13 @@
         <v>103</v>
       </c>
       <c r="C95" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E95" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="F95" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -5904,13 +5937,13 @@
         <v>104</v>
       </c>
       <c r="C96" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D96" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="F96" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -5918,7 +5951,7 @@
         <v>11</v>
       </c>
       <c r="F97" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -5929,16 +5962,16 @@
         <v>36</v>
       </c>
       <c r="C98" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D98" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="E98" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="F98" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -5949,13 +5982,13 @@
         <v>105</v>
       </c>
       <c r="C99" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D99" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="F99" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -5966,13 +5999,13 @@
         <v>106</v>
       </c>
       <c r="C100" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D100" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="F100" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -5983,13 +6016,13 @@
         <v>107</v>
       </c>
       <c r="C101" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D101" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="F101" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -6000,13 +6033,13 @@
         <v>108</v>
       </c>
       <c r="C102" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D102" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="F102" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -6017,13 +6050,13 @@
         <v>109</v>
       </c>
       <c r="C103" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E103" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="F103" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -6034,13 +6067,13 @@
         <v>46</v>
       </c>
       <c r="C104" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D104" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="F104" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -6051,13 +6084,13 @@
         <v>47</v>
       </c>
       <c r="C105" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D105" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="F105" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -6068,13 +6101,13 @@
         <v>46</v>
       </c>
       <c r="C106" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D106" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="F106" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -6085,13 +6118,13 @@
         <v>47</v>
       </c>
       <c r="C107" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D107" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="F107" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -6102,13 +6135,13 @@
         <v>48</v>
       </c>
       <c r="C108" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D108" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="F108" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -6119,13 +6152,13 @@
         <v>49</v>
       </c>
       <c r="C109" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D109" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="F109" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -6136,13 +6169,13 @@
         <v>50</v>
       </c>
       <c r="C110" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D110" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="F110" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -6153,13 +6186,13 @@
         <v>110</v>
       </c>
       <c r="C111" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E111" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="F111" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -6170,13 +6203,13 @@
         <v>111</v>
       </c>
       <c r="C112" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E112" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="F112" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -6187,13 +6220,13 @@
         <v>112</v>
       </c>
       <c r="C113" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E113" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="F113" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -6204,13 +6237,13 @@
         <v>113</v>
       </c>
       <c r="C114" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E114" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="F114" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -6221,13 +6254,13 @@
         <v>114</v>
       </c>
       <c r="C115" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E115" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="F115" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -6238,13 +6271,13 @@
         <v>115</v>
       </c>
       <c r="C116" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D116" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="F116" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -6255,13 +6288,13 @@
         <v>116</v>
       </c>
       <c r="C117" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D117" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="F117" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -6272,13 +6305,13 @@
         <v>117</v>
       </c>
       <c r="C118" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D118" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="F118" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -6289,13 +6322,13 @@
         <v>118</v>
       </c>
       <c r="C119" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D119" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="F119" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -6306,13 +6339,13 @@
         <v>119</v>
       </c>
       <c r="C120" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E120" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="F120" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -6323,13 +6356,13 @@
         <v>46</v>
       </c>
       <c r="C121" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D121" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="F121" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -6340,13 +6373,13 @@
         <v>47</v>
       </c>
       <c r="C122" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D122" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="F122" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -6357,13 +6390,13 @@
         <v>46</v>
       </c>
       <c r="C123" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D123" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="F123" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -6374,13 +6407,13 @@
         <v>47</v>
       </c>
       <c r="C124" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D124" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="F124" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -6391,13 +6424,13 @@
         <v>48</v>
       </c>
       <c r="C125" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D125" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="F125" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -6408,13 +6441,13 @@
         <v>49</v>
       </c>
       <c r="C126" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D126" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="F126" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -6425,13 +6458,13 @@
         <v>120</v>
       </c>
       <c r="C127" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E127" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="F127" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -6442,13 +6475,13 @@
         <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E128" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="F128" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -6459,13 +6492,13 @@
         <v>122</v>
       </c>
       <c r="C129" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E129" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="F129" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -6476,13 +6509,13 @@
         <v>123</v>
       </c>
       <c r="C130" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E130" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="F130" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -6493,13 +6526,13 @@
         <v>124</v>
       </c>
       <c r="C131" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E131" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="F131" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -6510,13 +6543,13 @@
         <v>125</v>
       </c>
       <c r="C132" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E132" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="F132" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -6527,13 +6560,13 @@
         <v>126</v>
       </c>
       <c r="C133" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E133" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="F133" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -6544,13 +6577,13 @@
         <v>127</v>
       </c>
       <c r="C134" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D134" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="F134" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -6561,13 +6594,13 @@
         <v>128</v>
       </c>
       <c r="C135" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D135" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="F135" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -6578,13 +6611,13 @@
         <v>129</v>
       </c>
       <c r="C136" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D136" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F136" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -6595,13 +6628,13 @@
         <v>130</v>
       </c>
       <c r="C137" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E137" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="F137" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -6612,13 +6645,13 @@
         <v>46</v>
       </c>
       <c r="C138" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D138" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F138" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -6629,13 +6662,13 @@
         <v>47</v>
       </c>
       <c r="C139" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D139" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="F139" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6646,13 +6679,13 @@
         <v>46</v>
       </c>
       <c r="C140" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D140" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="F140" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6663,13 +6696,13 @@
         <v>47</v>
       </c>
       <c r="C141" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D141" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="F141" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6680,13 +6713,13 @@
         <v>48</v>
       </c>
       <c r="C142" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D142" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="F142" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -6697,13 +6730,13 @@
         <v>49</v>
       </c>
       <c r="C143" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D143" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="F143" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6711,7 +6744,7 @@
         <v>14</v>
       </c>
       <c r="F144" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -6722,16 +6755,16 @@
         <v>36</v>
       </c>
       <c r="C145" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D145" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="E145" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="F145" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -6742,13 +6775,13 @@
         <v>131</v>
       </c>
       <c r="C146" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E146" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="F146" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -6759,13 +6792,13 @@
         <v>132</v>
       </c>
       <c r="C147" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E147" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="F147" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -6776,13 +6809,13 @@
         <v>133</v>
       </c>
       <c r="C148" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E148" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="F148" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -6793,13 +6826,13 @@
         <v>134</v>
       </c>
       <c r="C149" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E149" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="F149" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -6810,13 +6843,13 @@
         <v>135</v>
       </c>
       <c r="C150" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E150" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="F150" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -6827,13 +6860,13 @@
         <v>136</v>
       </c>
       <c r="C151" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E151" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="F151" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -6844,13 +6877,13 @@
         <v>137</v>
       </c>
       <c r="C152" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E152" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="F152" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -6861,13 +6894,13 @@
         <v>138</v>
       </c>
       <c r="C153" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E153" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="F153" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -6878,13 +6911,13 @@
         <v>139</v>
       </c>
       <c r="C154" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E154" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="F154" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -6895,13 +6928,13 @@
         <v>140</v>
       </c>
       <c r="C155" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E155" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="F155" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -6912,13 +6945,13 @@
         <v>141</v>
       </c>
       <c r="C156" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E156" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="F156" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -6929,13 +6962,13 @@
         <v>142</v>
       </c>
       <c r="C157" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E157" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="F157" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -6946,13 +6979,13 @@
         <v>143</v>
       </c>
       <c r="C158" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E158" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="F158" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -6963,13 +6996,13 @@
         <v>144</v>
       </c>
       <c r="C159" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E159" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="F159" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -6980,13 +7013,13 @@
         <v>145</v>
       </c>
       <c r="C160" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E160" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="F160" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -6997,13 +7030,13 @@
         <v>146</v>
       </c>
       <c r="C161" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D161" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="F161" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -7014,13 +7047,13 @@
         <v>147</v>
       </c>
       <c r="C162" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D162" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="F162" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -7031,13 +7064,13 @@
         <v>148</v>
       </c>
       <c r="C163" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D163" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="F163" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -7048,13 +7081,13 @@
         <v>149</v>
       </c>
       <c r="C164" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D164" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="F164" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -7065,13 +7098,13 @@
         <v>150</v>
       </c>
       <c r="C165" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E165" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="F165" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -7082,13 +7115,13 @@
         <v>46</v>
       </c>
       <c r="C166" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D166" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="F166" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -7099,13 +7132,13 @@
         <v>47</v>
       </c>
       <c r="C167" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D167" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="F167" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -7116,13 +7149,13 @@
         <v>48</v>
       </c>
       <c r="C168" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D168" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="F168" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -7133,13 +7166,13 @@
         <v>49</v>
       </c>
       <c r="C169" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D169" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="F169" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -7150,13 +7183,13 @@
         <v>151</v>
       </c>
       <c r="C170" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E170" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="F170" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -7167,13 +7200,13 @@
         <v>152</v>
       </c>
       <c r="C171" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E171" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="F171" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -7184,13 +7217,13 @@
         <v>153</v>
       </c>
       <c r="C172" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E172" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="F172" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -7201,13 +7234,13 @@
         <v>154</v>
       </c>
       <c r="C173" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E173" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="F173" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -7218,13 +7251,13 @@
         <v>155</v>
       </c>
       <c r="C174" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E174" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="F174" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -7235,13 +7268,13 @@
         <v>156</v>
       </c>
       <c r="C175" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E175" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="F175" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -7252,13 +7285,13 @@
         <v>157</v>
       </c>
       <c r="C176" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D176" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="F176" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -7269,13 +7302,13 @@
         <v>158</v>
       </c>
       <c r="C177" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D177" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="F177" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -7286,13 +7319,13 @@
         <v>159</v>
       </c>
       <c r="C178" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D178" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="F178" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -7303,13 +7336,13 @@
         <v>160</v>
       </c>
       <c r="C179" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E179" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="F179" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -7320,13 +7353,13 @@
         <v>46</v>
       </c>
       <c r="C180" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D180" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="F180" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -7337,13 +7370,13 @@
         <v>47</v>
       </c>
       <c r="C181" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D181" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="F181" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -7354,13 +7387,13 @@
         <v>46</v>
       </c>
       <c r="C182" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D182" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="F182" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -7371,13 +7404,13 @@
         <v>47</v>
       </c>
       <c r="C183" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D183" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="F183" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -7388,13 +7421,13 @@
         <v>46</v>
       </c>
       <c r="C184" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D184" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="F184" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -7405,13 +7438,13 @@
         <v>47</v>
       </c>
       <c r="C185" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D185" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="F185" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -7422,13 +7455,13 @@
         <v>48</v>
       </c>
       <c r="C186" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D186" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="F186" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -7439,13 +7472,13 @@
         <v>49</v>
       </c>
       <c r="C187" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D187" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="F187" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -7456,13 +7489,13 @@
         <v>161</v>
       </c>
       <c r="C188" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E188" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="F188" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -7473,13 +7506,13 @@
         <v>162</v>
       </c>
       <c r="C189" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E189" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="F189" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -7490,13 +7523,13 @@
         <v>163</v>
       </c>
       <c r="C190" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E190" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="F190" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -7504,7 +7537,7 @@
         <v>19</v>
       </c>
       <c r="F191" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -7515,16 +7548,16 @@
         <v>36</v>
       </c>
       <c r="C192" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="E192" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="F192" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -7535,13 +7568,13 @@
         <v>164</v>
       </c>
       <c r="C193" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E193" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="F193" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -7552,13 +7585,13 @@
         <v>165</v>
       </c>
       <c r="C194" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E194" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="F194" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -7569,13 +7602,13 @@
         <v>166</v>
       </c>
       <c r="C195" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E195" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="F195" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -7586,13 +7619,13 @@
         <v>167</v>
       </c>
       <c r="C196" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E196" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="F196" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -7603,13 +7636,13 @@
         <v>168</v>
       </c>
       <c r="C197" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D197" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="F197" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -7620,13 +7653,13 @@
         <v>169</v>
       </c>
       <c r="C198" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D198" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="F198" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -7637,13 +7670,13 @@
         <v>170</v>
       </c>
       <c r="C199" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E199" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="F199" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -7654,13 +7687,13 @@
         <v>46</v>
       </c>
       <c r="C200" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D200" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="F200" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -7671,13 +7704,13 @@
         <v>47</v>
       </c>
       <c r="C201" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D201" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="F201" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -7688,13 +7721,13 @@
         <v>46</v>
       </c>
       <c r="C202" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D202" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="F202" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -7705,13 +7738,13 @@
         <v>47</v>
       </c>
       <c r="C203" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D203" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="F203" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -7722,13 +7755,13 @@
         <v>48</v>
       </c>
       <c r="C204" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D204" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="F204" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -7739,13 +7772,13 @@
         <v>49</v>
       </c>
       <c r="C205" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D205" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="F205" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -7756,13 +7789,13 @@
         <v>50</v>
       </c>
       <c r="C206" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D206" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="F206" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -7773,13 +7806,13 @@
         <v>171</v>
       </c>
       <c r="C207" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E207" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="F207" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -7790,13 +7823,13 @@
         <v>172</v>
       </c>
       <c r="C208" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E208" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="F208" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -7807,13 +7840,13 @@
         <v>173</v>
       </c>
       <c r="C209" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E209" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="F209" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -7824,13 +7857,13 @@
         <v>174</v>
       </c>
       <c r="C210" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E210" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="F210" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -7841,13 +7874,13 @@
         <v>175</v>
       </c>
       <c r="C211" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E211" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="F211" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -7858,13 +7891,13 @@
         <v>176</v>
       </c>
       <c r="C212" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D212" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="F212" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -7875,13 +7908,13 @@
         <v>177</v>
       </c>
       <c r="C213" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E213" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="F213" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -7892,13 +7925,13 @@
         <v>46</v>
       </c>
       <c r="C214" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D214" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="F214" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -7909,13 +7942,13 @@
         <v>47</v>
       </c>
       <c r="C215" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D215" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="F215" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -7926,13 +7959,13 @@
         <v>46</v>
       </c>
       <c r="C216" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D216" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="F216" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -7943,13 +7976,13 @@
         <v>47</v>
       </c>
       <c r="C217" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D217" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="F217" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -7960,13 +7993,13 @@
         <v>48</v>
       </c>
       <c r="C218" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D218" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="F218" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -7977,13 +8010,13 @@
         <v>49</v>
       </c>
       <c r="C219" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D219" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="F219" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -7994,13 +8027,13 @@
         <v>178</v>
       </c>
       <c r="C220" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E220" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="F220" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8011,13 +8044,13 @@
         <v>179</v>
       </c>
       <c r="C221" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E221" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="F221" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -8028,13 +8061,13 @@
         <v>180</v>
       </c>
       <c r="C222" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E222" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="F222" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -8045,13 +8078,13 @@
         <v>181</v>
       </c>
       <c r="C223" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E223" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="F223" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -8062,13 +8095,13 @@
         <v>182</v>
       </c>
       <c r="C224" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E224" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="F224" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -8079,13 +8112,13 @@
         <v>183</v>
       </c>
       <c r="C225" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E225" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="F225" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -8096,13 +8129,13 @@
         <v>184</v>
       </c>
       <c r="C226" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E226" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="F226" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -8113,13 +8146,13 @@
         <v>185</v>
       </c>
       <c r="C227" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E227" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="F227" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -8130,13 +8163,13 @@
         <v>186</v>
       </c>
       <c r="C228" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E228" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="F228" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -8147,13 +8180,13 @@
         <v>187</v>
       </c>
       <c r="C229" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D229" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="F229" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -8164,13 +8197,13 @@
         <v>188</v>
       </c>
       <c r="C230" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="E230" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="F230" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -8181,13 +8214,13 @@
         <v>46</v>
       </c>
       <c r="C231" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D231" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="F231" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -8198,13 +8231,13 @@
         <v>47</v>
       </c>
       <c r="C232" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D232" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="F232" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -8215,13 +8248,13 @@
         <v>46</v>
       </c>
       <c r="C233" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D233" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="F233" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -8232,13 +8265,13 @@
         <v>47</v>
       </c>
       <c r="C234" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D234" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="F234" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -8249,13 +8282,13 @@
         <v>46</v>
       </c>
       <c r="C235" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D235" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="F235" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -8266,13 +8299,13 @@
         <v>47</v>
       </c>
       <c r="C236" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D236" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="F236" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -8283,13 +8316,13 @@
         <v>48</v>
       </c>
       <c r="C237" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D237" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="F237" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -8297,7 +8330,7 @@
         <v>22</v>
       </c>
       <c r="F238" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -8308,16 +8341,16 @@
         <v>36</v>
       </c>
       <c r="C239" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D239" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="E239" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="F239" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -8328,30 +8361,30 @@
         <v>49</v>
       </c>
       <c r="C240" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D240" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="F240" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B241" t="s">
         <v>189</v>
       </c>
       <c r="C241" t="s">
-        <v>485</v>
-      </c>
-      <c r="E241" t="s">
-        <v>915</v>
+        <v>488</v>
+      </c>
+      <c r="D241" t="s">
+        <v>738</v>
       </c>
       <c r="F241" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -8362,13 +8395,13 @@
         <v>190</v>
       </c>
       <c r="C242" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E242" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="F242" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -8379,13 +8412,13 @@
         <v>191</v>
       </c>
       <c r="C243" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E243" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="F243" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -8396,13 +8429,13 @@
         <v>192</v>
       </c>
       <c r="C244" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E244" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="F244" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -8413,13 +8446,13 @@
         <v>193</v>
       </c>
       <c r="C245" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E245" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="F245" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="246" spans="1:6">
@@ -8430,13 +8463,13 @@
         <v>194</v>
       </c>
       <c r="C246" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E246" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="F246" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -8447,13 +8480,13 @@
         <v>195</v>
       </c>
       <c r="C247" t="s">
-        <v>491</v>
-      </c>
-      <c r="D247" t="s">
-        <v>732</v>
+        <v>494</v>
+      </c>
+      <c r="E247" t="s">
+        <v>927</v>
       </c>
       <c r="F247" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="248" spans="1:6">
@@ -8464,13 +8497,13 @@
         <v>196</v>
       </c>
       <c r="C248" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D248" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="F248" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -8481,13 +8514,13 @@
         <v>197</v>
       </c>
       <c r="C249" t="s">
-        <v>493</v>
-      </c>
-      <c r="E249" t="s">
-        <v>920</v>
+        <v>496</v>
+      </c>
+      <c r="D249" t="s">
+        <v>740</v>
       </c>
       <c r="F249" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -8495,16 +8528,16 @@
         <v>23</v>
       </c>
       <c r="B250" t="s">
-        <v>46</v>
+        <v>198</v>
       </c>
       <c r="C250" t="s">
-        <v>494</v>
-      </c>
-      <c r="D250" t="s">
-        <v>734</v>
+        <v>497</v>
+      </c>
+      <c r="E250" t="s">
+        <v>928</v>
       </c>
       <c r="F250" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -8512,16 +8545,16 @@
         <v>23</v>
       </c>
       <c r="B251" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C251" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D251" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="F251" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -8529,16 +8562,16 @@
         <v>23</v>
       </c>
       <c r="B252" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C252" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D252" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="F252" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -8546,16 +8579,16 @@
         <v>23</v>
       </c>
       <c r="B253" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C253" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D253" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="F253" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -8563,16 +8596,16 @@
         <v>23</v>
       </c>
       <c r="B254" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C254" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D254" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="F254" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -8580,33 +8613,33 @@
         <v>23</v>
       </c>
       <c r="B255" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C255" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D255" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="F255" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B256" t="s">
-        <v>198</v>
+        <v>49</v>
       </c>
       <c r="C256" t="s">
-        <v>500</v>
-      </c>
-      <c r="E256" t="s">
-        <v>921</v>
+        <v>503</v>
+      </c>
+      <c r="D256" t="s">
+        <v>746</v>
       </c>
       <c r="F256" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -8617,13 +8650,13 @@
         <v>199</v>
       </c>
       <c r="C257" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E257" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="F257" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -8634,13 +8667,13 @@
         <v>200</v>
       </c>
       <c r="C258" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E258" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="F258" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -8651,13 +8684,13 @@
         <v>201</v>
       </c>
       <c r="C259" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E259" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="F259" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -8668,13 +8701,13 @@
         <v>202</v>
       </c>
       <c r="C260" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E260" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="F260" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -8685,13 +8718,13 @@
         <v>203</v>
       </c>
       <c r="C261" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E261" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="F261" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -8702,13 +8735,13 @@
         <v>204</v>
       </c>
       <c r="C262" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E262" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="F262" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -8719,13 +8752,13 @@
         <v>205</v>
       </c>
       <c r="C263" t="s">
-        <v>507</v>
-      </c>
-      <c r="D263" t="s">
-        <v>740</v>
+        <v>510</v>
+      </c>
+      <c r="E263" t="s">
+        <v>935</v>
       </c>
       <c r="F263" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -8736,13 +8769,13 @@
         <v>206</v>
       </c>
       <c r="C264" t="s">
-        <v>508</v>
-      </c>
-      <c r="E264" t="s">
-        <v>928</v>
+        <v>511</v>
+      </c>
+      <c r="D264" t="s">
+        <v>747</v>
       </c>
       <c r="F264" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -8750,16 +8783,16 @@
         <v>24</v>
       </c>
       <c r="B265" t="s">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="C265" t="s">
-        <v>509</v>
-      </c>
-      <c r="D265" t="s">
-        <v>741</v>
+        <v>512</v>
+      </c>
+      <c r="E265" t="s">
+        <v>936</v>
       </c>
       <c r="F265" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -8767,16 +8800,16 @@
         <v>24</v>
       </c>
       <c r="B266" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C266" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D266" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="F266" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -8784,16 +8817,16 @@
         <v>24</v>
       </c>
       <c r="B267" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C267" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D267" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="F267" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -8801,16 +8834,16 @@
         <v>24</v>
       </c>
       <c r="B268" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C268" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D268" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="F268" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -8818,16 +8851,16 @@
         <v>24</v>
       </c>
       <c r="B269" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C269" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D269" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="F269" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -8835,16 +8868,16 @@
         <v>24</v>
       </c>
       <c r="B270" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="C270" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D270" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="F270" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -8852,16 +8885,16 @@
         <v>24</v>
       </c>
       <c r="B271" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C271" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D271" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="F271" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -8869,16 +8902,16 @@
         <v>24</v>
       </c>
       <c r="B272" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C272" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D272" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="F272" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="273" spans="1:6">
@@ -8886,33 +8919,33 @@
         <v>24</v>
       </c>
       <c r="B273" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C273" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D273" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="F273" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B274" t="s">
-        <v>207</v>
+        <v>49</v>
       </c>
       <c r="C274" t="s">
-        <v>518</v>
-      </c>
-      <c r="E274" t="s">
-        <v>929</v>
+        <v>521</v>
+      </c>
+      <c r="D274" t="s">
+        <v>756</v>
       </c>
       <c r="F274" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -8923,13 +8956,13 @@
         <v>208</v>
       </c>
       <c r="C275" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E275" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="F275" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -8940,13 +8973,13 @@
         <v>209</v>
       </c>
       <c r="C276" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E276" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="F276" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -8957,13 +8990,13 @@
         <v>210</v>
       </c>
       <c r="C277" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E277" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="F277" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -8974,13 +9007,13 @@
         <v>211</v>
       </c>
       <c r="C278" t="s">
-        <v>522</v>
-      </c>
-      <c r="D278" t="s">
-        <v>750</v>
+        <v>525</v>
+      </c>
+      <c r="E278" t="s">
+        <v>940</v>
       </c>
       <c r="F278" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -8991,13 +9024,13 @@
         <v>212</v>
       </c>
       <c r="C279" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D279" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="F279" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -9008,13 +9041,13 @@
         <v>213</v>
       </c>
       <c r="C280" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D280" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="F280" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -9025,13 +9058,13 @@
         <v>214</v>
       </c>
       <c r="C281" t="s">
-        <v>525</v>
-      </c>
-      <c r="E281" t="s">
-        <v>933</v>
+        <v>528</v>
+      </c>
+      <c r="D281" t="s">
+        <v>759</v>
       </c>
       <c r="F281" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -9039,16 +9072,16 @@
         <v>25</v>
       </c>
       <c r="B282" t="s">
-        <v>46</v>
+        <v>215</v>
       </c>
       <c r="C282" t="s">
-        <v>526</v>
-      </c>
-      <c r="D282" t="s">
-        <v>753</v>
+        <v>529</v>
+      </c>
+      <c r="E282" t="s">
+        <v>941</v>
       </c>
       <c r="F282" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -9056,16 +9089,16 @@
         <v>25</v>
       </c>
       <c r="B283" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C283" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D283" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="F283" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -9073,16 +9106,16 @@
         <v>25</v>
       </c>
       <c r="B284" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C284" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D284" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="F284" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -9090,7 +9123,7 @@
         <v>26</v>
       </c>
       <c r="F285" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -9101,16 +9134,16 @@
         <v>36</v>
       </c>
       <c r="C286" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D286" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="E286" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="F286" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -9118,16 +9151,16 @@
         <v>25</v>
       </c>
       <c r="B287" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C287" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D287" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="F287" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -9135,33 +9168,33 @@
         <v>25</v>
       </c>
       <c r="B288" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C288" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D288" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="F288" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B289" t="s">
-        <v>215</v>
+        <v>50</v>
       </c>
       <c r="C289" t="s">
-        <v>531</v>
-      </c>
-      <c r="E289" t="s">
-        <v>934</v>
+        <v>534</v>
+      </c>
+      <c r="D289" t="s">
+        <v>764</v>
       </c>
       <c r="F289" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -9172,13 +9205,13 @@
         <v>216</v>
       </c>
       <c r="C290" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E290" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="F290" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="291" spans="1:6">
@@ -9189,13 +9222,13 @@
         <v>217</v>
       </c>
       <c r="C291" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E291" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="F291" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="292" spans="1:6">
@@ -9206,13 +9239,13 @@
         <v>218</v>
       </c>
       <c r="C292" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E292" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="F292" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -9223,13 +9256,13 @@
         <v>219</v>
       </c>
       <c r="C293" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E293" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="F293" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -9240,13 +9273,13 @@
         <v>220</v>
       </c>
       <c r="C294" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E294" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="F294" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="295" spans="1:6">
@@ -9257,13 +9290,13 @@
         <v>221</v>
       </c>
       <c r="C295" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E295" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="F295" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -9274,13 +9307,13 @@
         <v>222</v>
       </c>
       <c r="C296" t="s">
-        <v>538</v>
-      </c>
-      <c r="D296" t="s">
-        <v>758</v>
+        <v>541</v>
+      </c>
+      <c r="E296" t="s">
+        <v>948</v>
       </c>
       <c r="F296" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="297" spans="1:6">
@@ -9291,13 +9324,13 @@
         <v>223</v>
       </c>
       <c r="C297" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D297" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="F297" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -9308,13 +9341,13 @@
         <v>224</v>
       </c>
       <c r="C298" t="s">
-        <v>540</v>
-      </c>
-      <c r="E298" t="s">
-        <v>941</v>
+        <v>543</v>
+      </c>
+      <c r="D298" t="s">
+        <v>766</v>
       </c>
       <c r="F298" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="299" spans="1:6">
@@ -9322,16 +9355,16 @@
         <v>27</v>
       </c>
       <c r="B299" t="s">
-        <v>46</v>
+        <v>225</v>
       </c>
       <c r="C299" t="s">
-        <v>541</v>
-      </c>
-      <c r="D299" t="s">
-        <v>760</v>
+        <v>544</v>
+      </c>
+      <c r="E299" t="s">
+        <v>949</v>
       </c>
       <c r="F299" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -9339,16 +9372,16 @@
         <v>27</v>
       </c>
       <c r="B300" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C300" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D300" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F300" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="301" spans="1:6">
@@ -9356,16 +9389,16 @@
         <v>27</v>
       </c>
       <c r="B301" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C301" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D301" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="F301" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -9373,16 +9406,16 @@
         <v>27</v>
       </c>
       <c r="B302" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C302" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D302" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="F302" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="303" spans="1:6">
@@ -9390,16 +9423,16 @@
         <v>27</v>
       </c>
       <c r="B303" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C303" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D303" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="F303" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="304" spans="1:6">
@@ -9407,50 +9440,50 @@
         <v>27</v>
       </c>
       <c r="B304" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C304" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D304" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="F304" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="305" spans="1:6">
       <c r="A305" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B305" t="s">
-        <v>225</v>
+        <v>49</v>
       </c>
       <c r="C305" t="s">
-        <v>547</v>
-      </c>
-      <c r="E305" t="s">
-        <v>942</v>
+        <v>550</v>
+      </c>
+      <c r="D305" t="s">
+        <v>772</v>
       </c>
       <c r="F305" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="306" spans="1:6">
       <c r="A306" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B306" t="s">
         <v>226</v>
       </c>
       <c r="C306" t="s">
-        <v>548</v>
-      </c>
-      <c r="E306" t="s">
-        <v>943</v>
+        <v>551</v>
+      </c>
+      <c r="D306" t="s">
+        <v>773</v>
       </c>
       <c r="F306" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="307" spans="1:6">
@@ -9461,13 +9494,13 @@
         <v>227</v>
       </c>
       <c r="C307" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E307" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F307" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -9478,13 +9511,13 @@
         <v>228</v>
       </c>
       <c r="C308" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E308" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="F308" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="309" spans="1:6">
@@ -9495,13 +9528,13 @@
         <v>229</v>
       </c>
       <c r="C309" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E309" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="F309" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -9512,13 +9545,13 @@
         <v>230</v>
       </c>
       <c r="C310" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E310" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="F310" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -9529,13 +9562,13 @@
         <v>231</v>
       </c>
       <c r="C311" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E311" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="F311" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -9546,13 +9579,13 @@
         <v>232</v>
       </c>
       <c r="C312" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E312" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="F312" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="313" spans="1:6">
@@ -9563,13 +9596,13 @@
         <v>233</v>
       </c>
       <c r="C313" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E313" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="F313" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="314" spans="1:6">
@@ -9577,16 +9610,16 @@
         <v>28</v>
       </c>
       <c r="B314" t="s">
-        <v>46</v>
+        <v>234</v>
       </c>
       <c r="C314" t="s">
-        <v>556</v>
-      </c>
-      <c r="D314" t="s">
-        <v>766</v>
+        <v>559</v>
+      </c>
+      <c r="E314" t="s">
+        <v>957</v>
       </c>
       <c r="F314" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="315" spans="1:6">
@@ -9594,16 +9627,16 @@
         <v>28</v>
       </c>
       <c r="B315" t="s">
-        <v>47</v>
+        <v>235</v>
       </c>
       <c r="C315" t="s">
-        <v>557</v>
-      </c>
-      <c r="D315" t="s">
-        <v>767</v>
+        <v>560</v>
+      </c>
+      <c r="E315" t="s">
+        <v>958</v>
       </c>
       <c r="F315" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -9614,13 +9647,13 @@
         <v>46</v>
       </c>
       <c r="C316" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D316" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="F316" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -9631,13 +9664,13 @@
         <v>47</v>
       </c>
       <c r="C317" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D317" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="F317" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -9645,16 +9678,16 @@
         <v>28</v>
       </c>
       <c r="B318" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C318" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D318" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="F318" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -9662,16 +9695,16 @@
         <v>28</v>
       </c>
       <c r="B319" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C319" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D319" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="F319" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -9679,50 +9712,50 @@
         <v>28</v>
       </c>
       <c r="B320" t="s">
-        <v>234</v>
+        <v>48</v>
       </c>
       <c r="C320" t="s">
-        <v>562</v>
-      </c>
-      <c r="E320" t="s">
-        <v>951</v>
+        <v>565</v>
+      </c>
+      <c r="D320" t="s">
+        <v>778</v>
       </c>
       <c r="F320" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="321" spans="1:6">
       <c r="A321" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B321" t="s">
-        <v>235</v>
+        <v>49</v>
       </c>
       <c r="C321" t="s">
-        <v>563</v>
-      </c>
-      <c r="E321" t="s">
-        <v>952</v>
+        <v>566</v>
+      </c>
+      <c r="D321" t="s">
+        <v>779</v>
       </c>
       <c r="F321" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="322" spans="1:6">
       <c r="A322" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B322" t="s">
         <v>236</v>
       </c>
       <c r="C322" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E322" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="F322" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -9733,13 +9766,13 @@
         <v>237</v>
       </c>
       <c r="C323" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E323" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="F323" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -9750,13 +9783,13 @@
         <v>238</v>
       </c>
       <c r="C324" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E324" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="F324" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -9767,13 +9800,13 @@
         <v>239</v>
       </c>
       <c r="C325" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E325" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="F325" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -9784,13 +9817,13 @@
         <v>240</v>
       </c>
       <c r="C326" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E326" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="F326" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -9801,13 +9834,13 @@
         <v>241</v>
       </c>
       <c r="C327" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E327" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="F327" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -9818,13 +9851,13 @@
         <v>242</v>
       </c>
       <c r="C328" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E328" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="F328" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -9835,13 +9868,13 @@
         <v>243</v>
       </c>
       <c r="C329" t="s">
-        <v>571</v>
-      </c>
-      <c r="D329" t="s">
-        <v>772</v>
+        <v>574</v>
+      </c>
+      <c r="E329" t="s">
+        <v>966</v>
       </c>
       <c r="F329" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -9852,13 +9885,13 @@
         <v>244</v>
       </c>
       <c r="C330" t="s">
-        <v>572</v>
-      </c>
-      <c r="D330" t="s">
-        <v>773</v>
+        <v>575</v>
+      </c>
+      <c r="E330" t="s">
+        <v>967</v>
       </c>
       <c r="F330" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="331" spans="1:6">
@@ -9869,13 +9902,13 @@
         <v>245</v>
       </c>
       <c r="C331" t="s">
-        <v>573</v>
-      </c>
-      <c r="E331" t="s">
-        <v>960</v>
+        <v>576</v>
+      </c>
+      <c r="D331" t="s">
+        <v>780</v>
       </c>
       <c r="F331" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -9883,7 +9916,7 @@
         <v>30</v>
       </c>
       <c r="F332" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -9894,16 +9927,16 @@
         <v>36</v>
       </c>
       <c r="C333" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D333" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="E333" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="F333" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -9911,16 +9944,16 @@
         <v>29</v>
       </c>
       <c r="B334" t="s">
-        <v>46</v>
+        <v>246</v>
       </c>
       <c r="C334" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D334" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="F334" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -9928,16 +9961,16 @@
         <v>29</v>
       </c>
       <c r="B335" t="s">
-        <v>47</v>
+        <v>247</v>
       </c>
       <c r="C335" t="s">
-        <v>575</v>
-      </c>
-      <c r="D335" t="s">
-        <v>775</v>
+        <v>578</v>
+      </c>
+      <c r="E335" t="s">
+        <v>968</v>
       </c>
       <c r="F335" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="336" spans="1:6">
@@ -9948,13 +9981,13 @@
         <v>46</v>
       </c>
       <c r="C336" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D336" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="F336" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="337" spans="1:6">
@@ -9965,13 +9998,13 @@
         <v>47</v>
       </c>
       <c r="C337" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D337" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="F337" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -9982,13 +10015,13 @@
         <v>46</v>
       </c>
       <c r="C338" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D338" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="F338" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="339" spans="1:6">
@@ -9999,13 +10032,13 @@
         <v>47</v>
       </c>
       <c r="C339" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D339" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="F339" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="340" spans="1:6">
@@ -10013,16 +10046,16 @@
         <v>29</v>
       </c>
       <c r="B340" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C340" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D340" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="F340" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="341" spans="1:6">
@@ -10030,67 +10063,67 @@
         <v>29</v>
       </c>
       <c r="B341" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C341" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D341" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="F341" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="342" spans="1:6">
       <c r="A342" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B342" t="s">
-        <v>246</v>
+        <v>48</v>
       </c>
       <c r="C342" t="s">
-        <v>582</v>
-      </c>
-      <c r="E342" t="s">
-        <v>961</v>
+        <v>585</v>
+      </c>
+      <c r="D342" t="s">
+        <v>788</v>
       </c>
       <c r="F342" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="343" spans="1:6">
       <c r="A343" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B343" t="s">
-        <v>247</v>
+        <v>49</v>
       </c>
       <c r="C343" t="s">
-        <v>583</v>
-      </c>
-      <c r="E343" t="s">
-        <v>962</v>
+        <v>586</v>
+      </c>
+      <c r="D343" t="s">
+        <v>789</v>
       </c>
       <c r="F343" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="344" spans="1:6">
       <c r="A344" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B344" t="s">
         <v>248</v>
       </c>
       <c r="C344" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E344" t="s">
-        <v>963</v>
+        <v>773</v>
       </c>
       <c r="F344" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -10101,13 +10134,13 @@
         <v>249</v>
       </c>
       <c r="C345" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E345" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="F345" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="346" spans="1:6">
@@ -10118,13 +10151,13 @@
         <v>250</v>
       </c>
       <c r="C346" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E346" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="F346" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="347" spans="1:6">
@@ -10132,16 +10165,16 @@
         <v>31</v>
       </c>
       <c r="B347" t="s">
-        <v>46</v>
+        <v>251</v>
       </c>
       <c r="C347" t="s">
-        <v>587</v>
-      </c>
-      <c r="D347" t="s">
-        <v>782</v>
+        <v>590</v>
+      </c>
+      <c r="E347" t="s">
+        <v>971</v>
       </c>
       <c r="F347" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="348" spans="1:6">
@@ -10149,16 +10182,16 @@
         <v>31</v>
       </c>
       <c r="B348" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
       <c r="C348" t="s">
-        <v>588</v>
-      </c>
-      <c r="D348" t="s">
-        <v>783</v>
+        <v>591</v>
+      </c>
+      <c r="E348" t="s">
+        <v>972</v>
       </c>
       <c r="F348" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="349" spans="1:6">
@@ -10166,16 +10199,16 @@
         <v>31</v>
       </c>
       <c r="B349" t="s">
-        <v>46</v>
+        <v>253</v>
       </c>
       <c r="C349" t="s">
-        <v>589</v>
-      </c>
-      <c r="D349" t="s">
-        <v>784</v>
+        <v>592</v>
+      </c>
+      <c r="E349" t="s">
+        <v>973</v>
       </c>
       <c r="F349" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="350" spans="1:6">
@@ -10183,16 +10216,16 @@
         <v>31</v>
       </c>
       <c r="B350" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C350" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D350" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="F350" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="351" spans="1:6">
@@ -10200,16 +10233,16 @@
         <v>31</v>
       </c>
       <c r="B351" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C351" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D351" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="F351" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="352" spans="1:6">
@@ -10217,16 +10250,16 @@
         <v>31</v>
       </c>
       <c r="B352" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C352" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D352" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="F352" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="353" spans="1:6">
@@ -10234,67 +10267,67 @@
         <v>31</v>
       </c>
       <c r="B353" t="s">
-        <v>251</v>
+        <v>47</v>
       </c>
       <c r="C353" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D353" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="F353" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="354" spans="1:6">
       <c r="A354" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B354" t="s">
-        <v>252</v>
+        <v>48</v>
       </c>
       <c r="C354" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D354" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="F354" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="355" spans="1:6">
       <c r="A355" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B355" t="s">
-        <v>253</v>
+        <v>49</v>
       </c>
       <c r="C355" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D355" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="F355" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="356" spans="1:6">
       <c r="A356" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B356" t="s">
         <v>254</v>
       </c>
       <c r="C356" t="s">
-        <v>596</v>
-      </c>
-      <c r="E356" t="s">
-        <v>966</v>
+        <v>599</v>
+      </c>
+      <c r="D356" t="s">
+        <v>796</v>
       </c>
       <c r="F356" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="357" spans="1:6">
@@ -10302,16 +10335,16 @@
         <v>32</v>
       </c>
       <c r="B357" t="s">
-        <v>46</v>
+        <v>255</v>
       </c>
       <c r="C357" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D357" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="F357" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="358" spans="1:6">
@@ -10319,16 +10352,16 @@
         <v>32</v>
       </c>
       <c r="B358" t="s">
-        <v>47</v>
+        <v>256</v>
       </c>
       <c r="C358" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D358" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="F358" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="359" spans="1:6">
@@ -10336,16 +10369,16 @@
         <v>32</v>
       </c>
       <c r="B359" t="s">
-        <v>46</v>
+        <v>257</v>
       </c>
       <c r="C359" t="s">
-        <v>599</v>
-      </c>
-      <c r="D359" t="s">
-        <v>793</v>
+        <v>602</v>
+      </c>
+      <c r="E359" t="s">
+        <v>974</v>
       </c>
       <c r="F359" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="360" spans="1:6">
@@ -10353,16 +10386,16 @@
         <v>32</v>
       </c>
       <c r="B360" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C360" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D360" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="F360" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="361" spans="1:6">
@@ -10370,16 +10403,16 @@
         <v>32</v>
       </c>
       <c r="B361" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C361" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D361" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="F361" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="362" spans="1:6">
@@ -10387,16 +10420,16 @@
         <v>32</v>
       </c>
       <c r="B362" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C362" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D362" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="F362" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="363" spans="1:6">
@@ -10404,67 +10437,67 @@
         <v>32</v>
       </c>
       <c r="B363" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C363" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D363" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="F363" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="364" spans="1:6">
       <c r="A364" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B364" t="s">
-        <v>255</v>
+        <v>48</v>
       </c>
       <c r="C364" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="D364" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="F364" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="365" spans="1:6">
       <c r="A365" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B365" t="s">
-        <v>256</v>
+        <v>49</v>
       </c>
       <c r="C365" t="s">
-        <v>605</v>
-      </c>
-      <c r="E365" t="s">
-        <v>967</v>
+        <v>608</v>
+      </c>
+      <c r="D365" t="s">
+        <v>804</v>
       </c>
       <c r="F365" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B366" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C366" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D366" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="F366" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="367" spans="1:6">
@@ -10472,16 +10505,16 @@
         <v>33</v>
       </c>
       <c r="B367" t="s">
-        <v>47</v>
+        <v>258</v>
       </c>
       <c r="C367" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D367" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="F367" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="368" spans="1:6">
@@ -10489,16 +10522,16 @@
         <v>33</v>
       </c>
       <c r="B368" t="s">
-        <v>46</v>
+        <v>259</v>
       </c>
       <c r="C368" t="s">
-        <v>608</v>
-      </c>
-      <c r="D368" t="s">
-        <v>801</v>
+        <v>611</v>
+      </c>
+      <c r="E368" t="s">
+        <v>975</v>
       </c>
       <c r="F368" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="369" spans="1:6">
@@ -10506,16 +10539,16 @@
         <v>33</v>
       </c>
       <c r="B369" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C369" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D369" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="F369" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="370" spans="1:6">
@@ -10523,16 +10556,16 @@
         <v>33</v>
       </c>
       <c r="B370" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C370" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D370" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="F370" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="371" spans="1:6">
@@ -10540,16 +10573,16 @@
         <v>33</v>
       </c>
       <c r="B371" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C371" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D371" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="F371" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -10557,16 +10590,16 @@
         <v>33</v>
       </c>
       <c r="B372" t="s">
-        <v>257</v>
+        <v>47</v>
       </c>
       <c r="C372" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D372" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="F372" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="373" spans="1:6">
@@ -10574,25 +10607,76 @@
         <v>33</v>
       </c>
       <c r="B373" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C373" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D373" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="F373" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="374" spans="1:6">
       <c r="A374" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="B374" t="s">
+        <v>49</v>
+      </c>
+      <c r="C374" t="s">
+        <v>617</v>
+      </c>
+      <c r="D374" t="s">
+        <v>812</v>
+      </c>
+      <c r="F374" t="s">
+        <v>1332</v>
       </c>
     </row>
     <row r="375" spans="1:6">
       <c r="A375" t="s">
+        <v>33</v>
+      </c>
+      <c r="B375" t="s">
+        <v>260</v>
+      </c>
+      <c r="C375" t="s">
+        <v>618</v>
+      </c>
+      <c r="D375" t="s">
+        <v>813</v>
+      </c>
+      <c r="F375" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376" t="s">
+        <v>33</v>
+      </c>
+      <c r="B376" t="s">
+        <v>47</v>
+      </c>
+      <c r="C376" t="s">
+        <v>619</v>
+      </c>
+      <c r="D376" t="s">
+        <v>814</v>
+      </c>
+      <c r="F376" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="A377" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="A378" t="s">
         <v>35</v>
       </c>
     </row>
